--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -76,7 +76,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -114,7 +114,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -152,7 +152,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -190,7 +190,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -228,7 +228,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -2816,7 +2816,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId13"/>
 </worksheet>
@@ -2832,7 +2832,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId14"/>
 </worksheet>
@@ -2848,7 +2848,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId15"/>
 </worksheet>
@@ -2864,7 +2864,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId16"/>
 </worksheet>
@@ -2880,7 +2880,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId17"/>
 </worksheet>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -4,11 +4,6 @@
   <workbookPr date1904="false"/>
   <sheets>
     <sheet sheetId="1" name="Work Items" r:id="rId1"/>
-    <sheet sheetId="2" name="Aging Wip" r:id="rId2"/>
-    <sheet sheetId="3" name="Cfd Plot" r:id="rId3"/>
-    <sheet sheetId="4" name="Cycle Time Scatter" r:id="rId4"/>
-    <sheet sheetId="5" name="Forecasted Cfd Plot" r:id="rId5"/>
-    <sheet sheetId="6" name="Throughput Histogram" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -67,196 +62,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
   <sheetPr>
@@ -2804,84 +2609,4 @@
   <pageSetup/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId13"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId14"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId15"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId16"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId17"/>
-</worksheet>
 </file>
--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -4,6 +4,11 @@
   <workbookPr date1904="false"/>
   <sheets>
     <sheet sheetId="1" name="Work Items" r:id="rId1"/>
+    <sheet sheetId="2" name="Aging Wip" r:id="rId2"/>
+    <sheet sheetId="3" name="Cfd Plot" r:id="rId3"/>
+    <sheet sheetId="4" name="Cycle Time Scatter" r:id="rId4"/>
+    <sheet sheetId="5" name="Forecasted Cfd Plot" r:id="rId5"/>
+    <sheet sheetId="6" name="Throughput Histogram" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -62,6 +67,196 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
   <sheetPr>
@@ -2609,4 +2804,84 @@
   <pageSetup/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId13"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId14"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId15"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId16"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId17"/>
+</worksheet>
 </file>
--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -6,9 +6,10 @@
     <sheet sheetId="1" name="Work Items" r:id="rId1"/>
     <sheet sheetId="2" name="Aging Wip" r:id="rId2"/>
     <sheet sheetId="3" name="Cfd Plot" r:id="rId3"/>
-    <sheet sheetId="4" name="Cycle Time Scatter" r:id="rId4"/>
-    <sheet sheetId="5" name="Forecasted Cfd Plot" r:id="rId5"/>
-    <sheet sheetId="6" name="Throughput Histogram" r:id="rId6"/>
+    <sheet sheetId="4" name="Cycle Time Bands" r:id="rId4"/>
+    <sheet sheetId="5" name="Cycle Time Scatter" r:id="rId5"/>
+    <sheet sheetId="6" name="Forecasted Cfd Plot" r:id="rId6"/>
+    <sheet sheetId="7" name="Throughput Histogram" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -76,7 +77,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -85,7 +86,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -114,7 +115,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -123,7 +124,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -152,7 +153,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -161,7 +162,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -190,7 +191,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -199,7 +200,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -228,7 +229,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -237,7 +238,45 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5038725" cy="4667250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -262,7 +301,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="12.100000000000001" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -272,13 +311,16 @@
     <col width="14.3" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="14.3" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="15.400000000000002" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="22.0" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="16.5" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="17.6" min="11" max="11" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="12" max="12" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="13" max="13" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col width="13.200000000000001" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="11.0" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="7.700000000000001" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="22.0" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="12" max="12" bestFit="1" customWidth="1"/>
+    <col width="16.5" min="13" max="13" bestFit="1" customWidth="1"/>
+    <col width="17.6" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="16" max="16" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="17" max="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -319,35 +361,50 @@
       </c>
       <c r="H1" s="0" t="inlineStr">
         <is>
+          <t>YYYY-Week</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>YYYY-MM</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>YYYY</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
           <t>Cycle Time (days)</t>
         </is>
       </c>
-      <c r="I1" s="0" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>Current Age (days)</t>
         </is>
       </c>
-      <c r="J1" s="0" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 1 day</t>
         </is>
       </c>
-      <c r="K1" s="0" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 7 days</t>
         </is>
       </c>
-      <c r="L1" s="0" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 14 days</t>
         </is>
       </c>
-      <c r="M1" s="0" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 21 days</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 28 days</t>
         </is>
@@ -385,23 +442,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>2025-W44</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I2" s="0"/>
-      <c r="J2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L2" s="0"/>
       <c r="M2" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -437,23 +507,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>2025-W44</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I3" s="0"/>
-      <c r="J3" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L3" s="0"/>
       <c r="M3" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -489,23 +572,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>2025-W46</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="I4" s="0"/>
-      <c r="J4" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L4" s="0"/>
       <c r="M4" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -541,23 +637,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>2025-W47</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="I5" s="0"/>
-      <c r="J5" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L5" s="0"/>
       <c r="M5" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -593,23 +702,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>2025-W46</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="0"/>
-      <c r="J6" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L6" s="0"/>
       <c r="M6" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -645,23 +767,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>2025-W49</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="I7" s="0"/>
-      <c r="J7" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L7" s="0"/>
       <c r="M7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -697,23 +832,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>2025-W47</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I8" s="0"/>
-      <c r="J8" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L8" s="0"/>
       <c r="M8" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -749,23 +897,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>2025-W48</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="I9" s="0"/>
-      <c r="J9" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L9" s="0"/>
       <c r="M9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -801,23 +962,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K10" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="I10" s="0"/>
-      <c r="J10" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L10" s="0"/>
       <c r="M10" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -853,23 +1027,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I11" s="0"/>
-      <c r="J11" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L11" s="0"/>
       <c r="M11" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -905,23 +1092,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I12" s="0"/>
-      <c r="J12" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L12" s="0"/>
       <c r="M12" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -957,23 +1157,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="I13" s="0"/>
-      <c r="J13" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L13" s="0"/>
       <c r="M13" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1009,23 +1222,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>2025-W51</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I14" s="0"/>
-      <c r="J14" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L14" s="0"/>
       <c r="M14" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1061,23 +1287,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="I15" s="0"/>
-      <c r="J15" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L15" s="0"/>
       <c r="M15" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1113,23 +1352,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>2025-W51</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K16" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="0"/>
-      <c r="J16" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L16" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L16" s="0"/>
       <c r="M16" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1165,23 +1417,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>2025-W51</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K17" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I17" s="0"/>
-      <c r="J17" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L17" s="0"/>
       <c r="M17" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1217,23 +1482,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>2025-W52</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K18" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I18" s="0"/>
-      <c r="J18" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L18" s="0"/>
       <c r="M18" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1269,23 +1547,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K19" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="I19" s="0"/>
-      <c r="J19" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L19" s="0"/>
       <c r="M19" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1321,23 +1612,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K20" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="I20" s="0"/>
-      <c r="J20" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L20" s="0"/>
       <c r="M20" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1373,23 +1677,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K21" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="I21" s="0"/>
-      <c r="J21" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L21" s="0"/>
       <c r="M21" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1425,23 +1742,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H22" s="0" t="n">
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K22" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="I22" s="0"/>
-      <c r="J22" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L22" s="0"/>
       <c r="M22" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1477,23 +1807,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K23" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I23" s="0"/>
-      <c r="J23" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L23" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L23" s="0"/>
       <c r="M23" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1529,23 +1872,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K24" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I24" s="0"/>
-      <c r="J24" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L24" s="0"/>
       <c r="M24" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1581,23 +1937,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K25" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="I25" s="0"/>
-      <c r="J25" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L25" s="0"/>
       <c r="M25" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1633,23 +2002,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K26" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="I26" s="0"/>
-      <c r="J26" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L26" s="0"/>
       <c r="M26" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1685,23 +2067,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K27" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I27" s="0"/>
-      <c r="J27" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L27" s="0"/>
       <c r="M27" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1737,23 +2132,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K28" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="I28" s="0"/>
-      <c r="J28" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L28" s="0"/>
       <c r="M28" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1789,23 +2197,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K29" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="I29" s="0"/>
-      <c r="J29" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L29" s="0"/>
       <c r="M29" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1841,23 +2262,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H30" s="0" t="n">
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K30" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="I30" s="0"/>
-      <c r="J30" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L30" s="0"/>
       <c r="M30" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1893,23 +2327,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H31" s="0" t="n">
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K31" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I31" s="0"/>
-      <c r="J31" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L31" s="0"/>
       <c r="M31" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1945,23 +2392,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H32" s="0" t="n">
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K32" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I32" s="0"/>
-      <c r="J32" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L32" s="0"/>
       <c r="M32" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1997,23 +2457,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H33" s="0" t="n">
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K33" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="I33" s="0"/>
-      <c r="J33" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L33" s="0"/>
       <c r="M33" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2049,23 +2522,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H34" s="0" t="n">
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K34" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="I34" s="0"/>
-      <c r="J34" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L34" s="0"/>
       <c r="M34" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2101,23 +2587,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H35" s="0" t="n">
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I35" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K35" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="I35" s="0"/>
-      <c r="J35" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L35" s="0"/>
       <c r="M35" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P35" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2152,14 +2651,17 @@
         </is>
       </c>
       <c r="H36" s="0"/>
-      <c r="I36" s="0" t="n">
-        <v>65</v>
-      </c>
+      <c r="I36" s="0"/>
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
-      <c r="L36" s="0"/>
+      <c r="L36" s="0" t="n">
+        <v>66</v>
+      </c>
       <c r="M36" s="0"/>
       <c r="N36" s="0"/>
+      <c r="O36" s="0"/>
+      <c r="P36" s="0"/>
+      <c r="Q36" s="0"/>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
@@ -2193,23 +2695,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H37" s="0" t="n">
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K37" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I37" s="0"/>
-      <c r="J37" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L37" s="0"/>
       <c r="M37" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2244,14 +2759,17 @@
         </is>
       </c>
       <c r="H38" s="0"/>
-      <c r="I38" s="0" t="n">
-        <v>63</v>
-      </c>
+      <c r="I38" s="0"/>
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
-      <c r="L38" s="0"/>
+      <c r="L38" s="0" t="n">
+        <v>64</v>
+      </c>
       <c r="M38" s="0"/>
       <c r="N38" s="0"/>
+      <c r="O38" s="0"/>
+      <c r="P38" s="0"/>
+      <c r="Q38" s="0"/>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
@@ -2285,23 +2803,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H39" s="0" t="n">
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I39" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K39" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I39" s="0"/>
-      <c r="J39" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L39" s="0"/>
       <c r="M39" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2336,14 +2867,17 @@
         </is>
       </c>
       <c r="H40" s="0"/>
-      <c r="I40" s="0" t="n">
-        <v>60</v>
-      </c>
+      <c r="I40" s="0"/>
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
-      <c r="L40" s="0"/>
+      <c r="L40" s="0" t="n">
+        <v>61</v>
+      </c>
       <c r="M40" s="0"/>
       <c r="N40" s="0"/>
+      <c r="O40" s="0"/>
+      <c r="P40" s="0"/>
+      <c r="Q40" s="0"/>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
@@ -2377,23 +2911,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H41" s="0" t="n">
+      <c r="H41" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I41" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K41" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="I41" s="0"/>
-      <c r="J41" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K41" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L41" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L41" s="0"/>
       <c r="M41" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P41" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2428,14 +2975,17 @@
         </is>
       </c>
       <c r="H42" s="0"/>
-      <c r="I42" s="0" t="n">
-        <v>54</v>
-      </c>
+      <c r="I42" s="0"/>
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
-      <c r="L42" s="0"/>
+      <c r="L42" s="0" t="n">
+        <v>55</v>
+      </c>
       <c r="M42" s="0"/>
       <c r="N42" s="0"/>
+      <c r="O42" s="0"/>
+      <c r="P42" s="0"/>
+      <c r="Q42" s="0"/>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
@@ -2468,14 +3018,17 @@
         </is>
       </c>
       <c r="H43" s="0"/>
-      <c r="I43" s="0" t="n">
-        <v>51</v>
-      </c>
+      <c r="I43" s="0"/>
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
-      <c r="L43" s="0"/>
+      <c r="L43" s="0" t="n">
+        <v>52</v>
+      </c>
       <c r="M43" s="0"/>
       <c r="N43" s="0"/>
+      <c r="O43" s="0"/>
+      <c r="P43" s="0"/>
+      <c r="Q43" s="0"/>
     </row>
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
@@ -2508,14 +3061,17 @@
         </is>
       </c>
       <c r="H44" s="0"/>
-      <c r="I44" s="0" t="n">
-        <v>47</v>
-      </c>
+      <c r="I44" s="0"/>
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
-      <c r="L44" s="0"/>
+      <c r="L44" s="0" t="n">
+        <v>48</v>
+      </c>
       <c r="M44" s="0"/>
       <c r="N44" s="0"/>
+      <c r="O44" s="0"/>
+      <c r="P44" s="0"/>
+      <c r="Q44" s="0"/>
     </row>
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
@@ -2548,14 +3104,17 @@
         </is>
       </c>
       <c r="H45" s="0"/>
-      <c r="I45" s="0" t="n">
-        <v>46</v>
-      </c>
+      <c r="I45" s="0"/>
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
-      <c r="L45" s="0"/>
+      <c r="L45" s="0" t="n">
+        <v>47</v>
+      </c>
       <c r="M45" s="0"/>
       <c r="N45" s="0"/>
+      <c r="O45" s="0"/>
+      <c r="P45" s="0"/>
+      <c r="Q45" s="0"/>
     </row>
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
@@ -2588,14 +3147,17 @@
         </is>
       </c>
       <c r="H46" s="0"/>
-      <c r="I46" s="0" t="n">
-        <v>44</v>
-      </c>
+      <c r="I46" s="0"/>
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
-      <c r="L46" s="0"/>
+      <c r="L46" s="0" t="n">
+        <v>45</v>
+      </c>
       <c r="M46" s="0"/>
       <c r="N46" s="0"/>
+      <c r="O46" s="0"/>
+      <c r="P46" s="0"/>
+      <c r="Q46" s="0"/>
     </row>
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
@@ -2628,14 +3190,17 @@
         </is>
       </c>
       <c r="H47" s="0"/>
-      <c r="I47" s="0" t="n">
-        <v>40</v>
-      </c>
+      <c r="I47" s="0"/>
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
-      <c r="L47" s="0"/>
+      <c r="L47" s="0" t="n">
+        <v>41</v>
+      </c>
       <c r="M47" s="0"/>
       <c r="N47" s="0"/>
+      <c r="O47" s="0"/>
+      <c r="P47" s="0"/>
+      <c r="Q47" s="0"/>
     </row>
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
@@ -2668,14 +3233,17 @@
         </is>
       </c>
       <c r="H48" s="0"/>
-      <c r="I48" s="0" t="n">
-        <v>37</v>
-      </c>
+      <c r="I48" s="0"/>
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
-      <c r="L48" s="0"/>
+      <c r="L48" s="0" t="n">
+        <v>38</v>
+      </c>
       <c r="M48" s="0"/>
       <c r="N48" s="0"/>
+      <c r="O48" s="0"/>
+      <c r="P48" s="0"/>
+      <c r="Q48" s="0"/>
     </row>
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
@@ -2708,14 +3276,17 @@
         </is>
       </c>
       <c r="H49" s="0"/>
-      <c r="I49" s="0" t="n">
-        <v>29</v>
-      </c>
+      <c r="I49" s="0"/>
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
-      <c r="L49" s="0"/>
+      <c r="L49" s="0" t="n">
+        <v>30</v>
+      </c>
       <c r="M49" s="0"/>
       <c r="N49" s="0"/>
+      <c r="O49" s="0"/>
+      <c r="P49" s="0"/>
+      <c r="Q49" s="0"/>
     </row>
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
@@ -2748,14 +3319,17 @@
         </is>
       </c>
       <c r="H50" s="0"/>
-      <c r="I50" s="0" t="n">
-        <v>27</v>
-      </c>
+      <c r="I50" s="0"/>
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
-      <c r="L50" s="0"/>
+      <c r="L50" s="0" t="n">
+        <v>28</v>
+      </c>
       <c r="M50" s="0"/>
       <c r="N50" s="0"/>
+      <c r="O50" s="0"/>
+      <c r="P50" s="0"/>
+      <c r="Q50" s="0"/>
     </row>
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
@@ -2788,14 +3362,17 @@
         </is>
       </c>
       <c r="H51" s="0"/>
-      <c r="I51" s="0" t="n">
-        <v>22</v>
-      </c>
+      <c r="I51" s="0"/>
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
-      <c r="L51" s="0"/>
+      <c r="L51" s="0" t="n">
+        <v>23</v>
+      </c>
       <c r="M51" s="0"/>
       <c r="N51" s="0"/>
+      <c r="O51" s="0"/>
+      <c r="P51" s="0"/>
+      <c r="Q51" s="0"/>
     </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>
@@ -2818,7 +3395,7 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId13"/>
+  <drawing r:id="rId15"/>
 </worksheet>
 </file>
 
@@ -2834,7 +3411,7 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId14"/>
+  <drawing r:id="rId16"/>
 </worksheet>
 </file>
 
@@ -2850,7 +3427,7 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId15"/>
+  <drawing r:id="rId17"/>
 </worksheet>
 </file>
 
@@ -2866,7 +3443,7 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId16"/>
+  <drawing r:id="rId18"/>
 </worksheet>
 </file>
 
@@ -2882,6 +3459,22 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId17"/>
+  <drawing r:id="rId19"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId20"/>
 </worksheet>
 </file>
--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2655,7 +2655,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M36" s="0"/>
       <c r="N36" s="0"/>
@@ -2763,7 +2763,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M38" s="0"/>
       <c r="N38" s="0"/>
@@ -2871,7 +2871,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M40" s="0"/>
       <c r="N40" s="0"/>
@@ -2979,7 +2979,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M42" s="0"/>
       <c r="N42" s="0"/>
@@ -3022,7 +3022,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M43" s="0"/>
       <c r="N43" s="0"/>
@@ -3065,7 +3065,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M44" s="0"/>
       <c r="N44" s="0"/>
@@ -3108,7 +3108,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M45" s="0"/>
       <c r="N45" s="0"/>
@@ -3151,7 +3151,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M46" s="0"/>
       <c r="N46" s="0"/>
@@ -3194,7 +3194,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M47" s="0"/>
       <c r="N47" s="0"/>
@@ -3237,7 +3237,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M48" s="0"/>
       <c r="N48" s="0"/>
@@ -3280,7 +3280,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M49" s="0"/>
       <c r="N49" s="0"/>
@@ -3323,7 +3323,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M50" s="0"/>
       <c r="N50" s="0"/>
@@ -3366,7 +3366,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M51" s="0"/>
       <c r="N51" s="0"/>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2655,7 +2655,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M36" s="0"/>
       <c r="N36" s="0"/>
@@ -2763,7 +2763,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M38" s="0"/>
       <c r="N38" s="0"/>
@@ -2871,7 +2871,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M40" s="0"/>
       <c r="N40" s="0"/>
@@ -2979,7 +2979,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M42" s="0"/>
       <c r="N42" s="0"/>
@@ -3022,7 +3022,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M43" s="0"/>
       <c r="N43" s="0"/>
@@ -3065,7 +3065,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M44" s="0"/>
       <c r="N44" s="0"/>
@@ -3108,7 +3108,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M45" s="0"/>
       <c r="N45" s="0"/>
@@ -3151,7 +3151,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M46" s="0"/>
       <c r="N46" s="0"/>
@@ -3194,7 +3194,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M47" s="0"/>
       <c r="N47" s="0"/>
@@ -3237,7 +3237,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M48" s="0"/>
       <c r="N48" s="0"/>
@@ -3280,7 +3280,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M49" s="0"/>
       <c r="N49" s="0"/>
@@ -3323,7 +3323,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M50" s="0"/>
       <c r="N50" s="0"/>
@@ -3366,7 +3366,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M51" s="0"/>
       <c r="N51" s="0"/>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2655,7 +2655,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M36" s="0"/>
       <c r="N36" s="0"/>
@@ -2763,7 +2763,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M38" s="0"/>
       <c r="N38" s="0"/>
@@ -2871,7 +2871,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M40" s="0"/>
       <c r="N40" s="0"/>
@@ -2979,7 +2979,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M42" s="0"/>
       <c r="N42" s="0"/>
@@ -3022,7 +3022,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M43" s="0"/>
       <c r="N43" s="0"/>
@@ -3065,7 +3065,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M44" s="0"/>
       <c r="N44" s="0"/>
@@ -3108,7 +3108,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M45" s="0"/>
       <c r="N45" s="0"/>
@@ -3151,7 +3151,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M46" s="0"/>
       <c r="N46" s="0"/>
@@ -3194,7 +3194,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M47" s="0"/>
       <c r="N47" s="0"/>
@@ -3237,7 +3237,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M48" s="0"/>
       <c r="N48" s="0"/>
@@ -3280,7 +3280,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M49" s="0"/>
       <c r="N49" s="0"/>
@@ -3323,7 +3323,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M50" s="0"/>
       <c r="N50" s="0"/>
@@ -3366,7 +3366,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M51" s="0"/>
       <c r="N51" s="0"/>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2655,7 +2655,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M36" s="0"/>
       <c r="N36" s="0"/>
@@ -2763,7 +2763,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M38" s="0"/>
       <c r="N38" s="0"/>
@@ -2871,7 +2871,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M40" s="0"/>
       <c r="N40" s="0"/>
@@ -2979,7 +2979,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M42" s="0"/>
       <c r="N42" s="0"/>
@@ -3022,7 +3022,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M43" s="0"/>
       <c r="N43" s="0"/>
@@ -3065,7 +3065,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M44" s="0"/>
       <c r="N44" s="0"/>
@@ -3108,7 +3108,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M45" s="0"/>
       <c r="N45" s="0"/>
@@ -3151,7 +3151,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M46" s="0"/>
       <c r="N46" s="0"/>
@@ -3194,7 +3194,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M47" s="0"/>
       <c r="N47" s="0"/>
@@ -3237,7 +3237,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M48" s="0"/>
       <c r="N48" s="0"/>
@@ -3280,7 +3280,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M49" s="0"/>
       <c r="N49" s="0"/>
@@ -3323,7 +3323,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M50" s="0"/>
       <c r="N50" s="0"/>
@@ -3366,7 +3366,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M51" s="0"/>
       <c r="N51" s="0"/>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2655,7 +2655,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M36" s="0"/>
       <c r="N36" s="0"/>
@@ -2763,7 +2763,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M38" s="0"/>
       <c r="N38" s="0"/>
@@ -2871,7 +2871,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M40" s="0"/>
       <c r="N40" s="0"/>
@@ -2979,7 +2979,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M42" s="0"/>
       <c r="N42" s="0"/>
@@ -3022,7 +3022,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M43" s="0"/>
       <c r="N43" s="0"/>
@@ -3065,7 +3065,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M44" s="0"/>
       <c r="N44" s="0"/>
@@ -3108,7 +3108,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M45" s="0"/>
       <c r="N45" s="0"/>
@@ -3151,7 +3151,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M46" s="0"/>
       <c r="N46" s="0"/>
@@ -3194,7 +3194,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M47" s="0"/>
       <c r="N47" s="0"/>
@@ -3237,7 +3237,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M48" s="0"/>
       <c r="N48" s="0"/>
@@ -3280,7 +3280,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M49" s="0"/>
       <c r="N49" s="0"/>
@@ -3323,7 +3323,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M50" s="0"/>
       <c r="N50" s="0"/>
@@ -3366,7 +3366,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M51" s="0"/>
       <c r="N51" s="0"/>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2655,7 +2655,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M36" s="0"/>
       <c r="N36" s="0"/>
@@ -2763,7 +2763,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M38" s="0"/>
       <c r="N38" s="0"/>
@@ -2871,7 +2871,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M40" s="0"/>
       <c r="N40" s="0"/>
@@ -2979,7 +2979,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M42" s="0"/>
       <c r="N42" s="0"/>
@@ -3022,7 +3022,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M43" s="0"/>
       <c r="N43" s="0"/>
@@ -3065,7 +3065,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M44" s="0"/>
       <c r="N44" s="0"/>
@@ -3108,7 +3108,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M45" s="0"/>
       <c r="N45" s="0"/>
@@ -3151,7 +3151,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M46" s="0"/>
       <c r="N46" s="0"/>
@@ -3194,7 +3194,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M47" s="0"/>
       <c r="N47" s="0"/>
@@ -3237,7 +3237,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M48" s="0"/>
       <c r="N48" s="0"/>
@@ -3280,7 +3280,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M49" s="0"/>
       <c r="N49" s="0"/>
@@ -3323,7 +3323,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M50" s="0"/>
       <c r="N50" s="0"/>
@@ -3366,7 +3366,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M51" s="0"/>
       <c r="N51" s="0"/>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2655,7 +2655,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M36" s="0"/>
       <c r="N36" s="0"/>
@@ -2763,7 +2763,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M38" s="0"/>
       <c r="N38" s="0"/>
@@ -2871,7 +2871,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M40" s="0"/>
       <c r="N40" s="0"/>
@@ -2979,7 +2979,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M42" s="0"/>
       <c r="N42" s="0"/>
@@ -3022,7 +3022,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M43" s="0"/>
       <c r="N43" s="0"/>
@@ -3065,7 +3065,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M44" s="0"/>
       <c r="N44" s="0"/>
@@ -3108,7 +3108,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M45" s="0"/>
       <c r="N45" s="0"/>
@@ -3151,7 +3151,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M46" s="0"/>
       <c r="N46" s="0"/>
@@ -3194,7 +3194,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M47" s="0"/>
       <c r="N47" s="0"/>
@@ -3237,7 +3237,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M48" s="0"/>
       <c r="N48" s="0"/>
@@ -3280,7 +3280,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M49" s="0"/>
       <c r="N49" s="0"/>
@@ -3323,7 +3323,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M50" s="0"/>
       <c r="N50" s="0"/>
@@ -3366,7 +3366,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M51" s="0"/>
       <c r="N51" s="0"/>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -301,7 +301,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="12.100000000000001" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -316,11 +316,12 @@
     <col width="7.700000000000001" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="22.0" min="11" max="11" bestFit="1" customWidth="1"/>
     <col width="23.1" min="12" max="12" bestFit="1" customWidth="1"/>
-    <col width="16.5" min="13" max="13" bestFit="1" customWidth="1"/>
-    <col width="17.6" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="99.00000000000001" min="13" max="13" bestFit="1" customWidth="1"/>
+    <col width="16.5" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col width="17.6" min="15" max="15" bestFit="1" customWidth="1"/>
     <col width="18.700000000000003" min="16" max="16" bestFit="1" customWidth="1"/>
     <col width="18.700000000000003" min="17" max="17" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="18" max="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -386,25 +387,30 @@
       </c>
       <c r="M1" s="0" t="inlineStr">
         <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="N1" s="0" t="inlineStr">
+        <is>
           <t>Done ≤ 1 day</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 7 days</t>
         </is>
       </c>
-      <c r="O1" s="0" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 14 days</t>
         </is>
       </c>
-      <c r="P1" s="0" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 21 days</t>
         </is>
       </c>
-      <c r="Q1" s="0" t="inlineStr">
+      <c r="R1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 28 days</t>
         </is>
@@ -459,8 +465,10 @@
         <v>16</v>
       </c>
       <c r="L2" s="0"/>
-      <c r="M2" s="0" t="b">
-        <v>0</v>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N2" s="0" t="b">
         <v>0</v>
@@ -469,9 +477,12 @@
         <v>0</v>
       </c>
       <c r="P2" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -524,11 +535,13 @@
         <v>6</v>
       </c>
       <c r="L3" s="0"/>
-      <c r="M3" s="0" t="b">
-        <v>0</v>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N3" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="0" t="b">
         <v>1</v>
@@ -537,6 +550,9 @@
         <v>1</v>
       </c>
       <c r="Q3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -589,8 +605,10 @@
         <v>20</v>
       </c>
       <c r="L4" s="0"/>
-      <c r="M4" s="0" t="b">
-        <v>0</v>
+      <c r="M4" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N4" s="0" t="b">
         <v>0</v>
@@ -599,9 +617,12 @@
         <v>0</v>
       </c>
       <c r="P4" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -654,8 +675,10 @@
         <v>20</v>
       </c>
       <c r="L5" s="0"/>
-      <c r="M5" s="0" t="b">
-        <v>0</v>
+      <c r="M5" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N5" s="0" t="b">
         <v>0</v>
@@ -664,9 +687,12 @@
         <v>0</v>
       </c>
       <c r="P5" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -719,11 +745,13 @@
         <v>5</v>
       </c>
       <c r="L6" s="0"/>
-      <c r="M6" s="0" t="b">
-        <v>0</v>
+      <c r="M6" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N6" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="0" t="b">
         <v>1</v>
@@ -732,6 +760,9 @@
         <v>1</v>
       </c>
       <c r="Q6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -784,8 +815,10 @@
         <v>21</v>
       </c>
       <c r="L7" s="0"/>
-      <c r="M7" s="0" t="b">
-        <v>0</v>
+      <c r="M7" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N7" s="0" t="b">
         <v>0</v>
@@ -794,9 +827,12 @@
         <v>0</v>
       </c>
       <c r="P7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -849,11 +885,13 @@
         <v>7</v>
       </c>
       <c r="L8" s="0"/>
-      <c r="M8" s="0" t="b">
-        <v>0</v>
+      <c r="M8" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N8" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="0" t="b">
         <v>1</v>
@@ -862,6 +900,9 @@
         <v>1</v>
       </c>
       <c r="Q8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -914,19 +955,24 @@
         <v>9</v>
       </c>
       <c r="L9" s="0"/>
-      <c r="M9" s="0" t="b">
-        <v>0</v>
+      <c r="M9" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N9" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -979,8 +1025,10 @@
         <v>19</v>
       </c>
       <c r="L10" s="0"/>
-      <c r="M10" s="0" t="b">
-        <v>0</v>
+      <c r="M10" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N10" s="0" t="b">
         <v>0</v>
@@ -989,9 +1037,12 @@
         <v>0</v>
       </c>
       <c r="P10" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1044,8 +1095,10 @@
         <v>16</v>
       </c>
       <c r="L11" s="0"/>
-      <c r="M11" s="0" t="b">
-        <v>0</v>
+      <c r="M11" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N11" s="0" t="b">
         <v>0</v>
@@ -1054,9 +1107,12 @@
         <v>0</v>
       </c>
       <c r="P11" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1109,11 +1165,13 @@
         <v>6</v>
       </c>
       <c r="L12" s="0"/>
-      <c r="M12" s="0" t="b">
-        <v>0</v>
+      <c r="M12" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N12" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="0" t="b">
         <v>1</v>
@@ -1122,6 +1180,9 @@
         <v>1</v>
       </c>
       <c r="Q12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1174,8 +1235,10 @@
         <v>19</v>
       </c>
       <c r="L13" s="0"/>
-      <c r="M13" s="0" t="b">
-        <v>0</v>
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N13" s="0" t="b">
         <v>0</v>
@@ -1184,9 +1247,12 @@
         <v>0</v>
       </c>
       <c r="P13" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1239,8 +1305,10 @@
         <v>16</v>
       </c>
       <c r="L14" s="0"/>
-      <c r="M14" s="0" t="b">
-        <v>0</v>
+      <c r="M14" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N14" s="0" t="b">
         <v>0</v>
@@ -1249,9 +1317,12 @@
         <v>0</v>
       </c>
       <c r="P14" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1304,8 +1375,10 @@
         <v>15</v>
       </c>
       <c r="L15" s="0"/>
-      <c r="M15" s="0" t="b">
-        <v>0</v>
+      <c r="M15" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N15" s="0" t="b">
         <v>0</v>
@@ -1314,9 +1387,12 @@
         <v>0</v>
       </c>
       <c r="P15" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1369,11 +1445,13 @@
         <v>3</v>
       </c>
       <c r="L16" s="0"/>
-      <c r="M16" s="0" t="b">
-        <v>0</v>
+      <c r="M16" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N16" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="0" t="b">
         <v>1</v>
@@ -1382,6 +1460,9 @@
         <v>1</v>
       </c>
       <c r="Q16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1434,11 +1515,13 @@
         <v>5</v>
       </c>
       <c r="L17" s="0"/>
-      <c r="M17" s="0" t="b">
-        <v>0</v>
+      <c r="M17" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N17" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="0" t="b">
         <v>1</v>
@@ -1447,6 +1530,9 @@
         <v>1</v>
       </c>
       <c r="Q17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1499,19 +1585,24 @@
         <v>10</v>
       </c>
       <c r="L18" s="0"/>
-      <c r="M18" s="0" t="b">
-        <v>0</v>
+      <c r="M18" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N18" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O18" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1564,8 +1655,10 @@
         <v>17</v>
       </c>
       <c r="L19" s="0"/>
-      <c r="M19" s="0" t="b">
-        <v>0</v>
+      <c r="M19" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N19" s="0" t="b">
         <v>0</v>
@@ -1574,9 +1667,12 @@
         <v>0</v>
       </c>
       <c r="P19" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1629,8 +1725,10 @@
         <v>15</v>
       </c>
       <c r="L20" s="0"/>
-      <c r="M20" s="0" t="b">
-        <v>0</v>
+      <c r="M20" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N20" s="0" t="b">
         <v>0</v>
@@ -1639,9 +1737,12 @@
         <v>0</v>
       </c>
       <c r="P20" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1694,8 +1795,10 @@
         <v>19</v>
       </c>
       <c r="L21" s="0"/>
-      <c r="M21" s="0" t="b">
-        <v>0</v>
+      <c r="M21" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N21" s="0" t="b">
         <v>0</v>
@@ -1704,9 +1807,12 @@
         <v>0</v>
       </c>
       <c r="P21" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1759,19 +1865,24 @@
         <v>14</v>
       </c>
       <c r="L22" s="0"/>
-      <c r="M22" s="0" t="b">
-        <v>0</v>
+      <c r="M22" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N22" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O22" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1824,11 +1935,13 @@
         <v>7</v>
       </c>
       <c r="L23" s="0"/>
-      <c r="M23" s="0" t="b">
-        <v>0</v>
+      <c r="M23" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N23" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="0" t="b">
         <v>1</v>
@@ -1837,6 +1950,9 @@
         <v>1</v>
       </c>
       <c r="Q23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1889,8 +2005,10 @@
         <v>18</v>
       </c>
       <c r="L24" s="0"/>
-      <c r="M24" s="0" t="b">
-        <v>0</v>
+      <c r="M24" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N24" s="0" t="b">
         <v>0</v>
@@ -1899,9 +2017,12 @@
         <v>0</v>
       </c>
       <c r="P24" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1954,19 +2075,24 @@
         <v>14</v>
       </c>
       <c r="L25" s="0"/>
-      <c r="M25" s="0" t="b">
-        <v>0</v>
+      <c r="M25" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N25" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O25" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2019,8 +2145,10 @@
         <v>20</v>
       </c>
       <c r="L26" s="0"/>
-      <c r="M26" s="0" t="b">
-        <v>0</v>
+      <c r="M26" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N26" s="0" t="b">
         <v>0</v>
@@ -2029,9 +2157,12 @@
         <v>0</v>
       </c>
       <c r="P26" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2084,11 +2215,13 @@
         <v>5</v>
       </c>
       <c r="L27" s="0"/>
-      <c r="M27" s="0" t="b">
-        <v>0</v>
+      <c r="M27" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N27" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="0" t="b">
         <v>1</v>
@@ -2097,6 +2230,9 @@
         <v>1</v>
       </c>
       <c r="Q27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2149,19 +2285,24 @@
         <v>8</v>
       </c>
       <c r="L28" s="0"/>
-      <c r="M28" s="0" t="b">
-        <v>0</v>
+      <c r="M28" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N28" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O28" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2214,8 +2355,10 @@
         <v>21</v>
       </c>
       <c r="L29" s="0"/>
-      <c r="M29" s="0" t="b">
-        <v>0</v>
+      <c r="M29" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N29" s="0" t="b">
         <v>0</v>
@@ -2224,9 +2367,12 @@
         <v>0</v>
       </c>
       <c r="P29" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2279,8 +2425,10 @@
         <v>20</v>
       </c>
       <c r="L30" s="0"/>
-      <c r="M30" s="0" t="b">
-        <v>0</v>
+      <c r="M30" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N30" s="0" t="b">
         <v>0</v>
@@ -2289,9 +2437,12 @@
         <v>0</v>
       </c>
       <c r="P30" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2344,8 +2495,10 @@
         <v>18</v>
       </c>
       <c r="L31" s="0"/>
-      <c r="M31" s="0" t="b">
-        <v>0</v>
+      <c r="M31" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N31" s="0" t="b">
         <v>0</v>
@@ -2354,9 +2507,12 @@
         <v>0</v>
       </c>
       <c r="P31" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2409,19 +2565,24 @@
         <v>10</v>
       </c>
       <c r="L32" s="0"/>
-      <c r="M32" s="0" t="b">
-        <v>0</v>
+      <c r="M32" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N32" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O32" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2474,8 +2635,10 @@
         <v>17</v>
       </c>
       <c r="L33" s="0"/>
-      <c r="M33" s="0" t="b">
-        <v>0</v>
+      <c r="M33" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N33" s="0" t="b">
         <v>0</v>
@@ -2484,9 +2647,12 @@
         <v>0</v>
       </c>
       <c r="P33" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2539,8 +2705,10 @@
         <v>17</v>
       </c>
       <c r="L34" s="0"/>
-      <c r="M34" s="0" t="b">
-        <v>0</v>
+      <c r="M34" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N34" s="0" t="b">
         <v>0</v>
@@ -2549,9 +2717,12 @@
         <v>0</v>
       </c>
       <c r="P34" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2604,19 +2775,24 @@
         <v>13</v>
       </c>
       <c r="L35" s="0"/>
-      <c r="M35" s="0" t="b">
-        <v>0</v>
+      <c r="M35" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N35" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O35" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q35" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2657,11 +2833,16 @@
       <c r="L36" s="0" t="n">
         <v>73</v>
       </c>
-      <c r="M36" s="0"/>
+      <c r="M36" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N36" s="0"/>
       <c r="O36" s="0"/>
       <c r="P36" s="0"/>
       <c r="Q36" s="0"/>
+      <c r="R36" s="0"/>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
@@ -2712,8 +2893,10 @@
         <v>18</v>
       </c>
       <c r="L37" s="0"/>
-      <c r="M37" s="0" t="b">
-        <v>0</v>
+      <c r="M37" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N37" s="0" t="b">
         <v>0</v>
@@ -2722,9 +2905,12 @@
         <v>0</v>
       </c>
       <c r="P37" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2765,11 +2951,16 @@
       <c r="L38" s="0" t="n">
         <v>71</v>
       </c>
-      <c r="M38" s="0"/>
+      <c r="M38" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N38" s="0"/>
       <c r="O38" s="0"/>
       <c r="P38" s="0"/>
       <c r="Q38" s="0"/>
+      <c r="R38" s="0"/>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
@@ -2820,19 +3011,24 @@
         <v>10</v>
       </c>
       <c r="L39" s="0"/>
-      <c r="M39" s="0" t="b">
-        <v>0</v>
+      <c r="M39" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N39" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O39" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2873,11 +3069,16 @@
       <c r="L40" s="0" t="n">
         <v>68</v>
       </c>
-      <c r="M40" s="0"/>
+      <c r="M40" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N40" s="0"/>
       <c r="O40" s="0"/>
       <c r="P40" s="0"/>
       <c r="Q40" s="0"/>
+      <c r="R40" s="0"/>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
@@ -2928,11 +3129,13 @@
         <v>4</v>
       </c>
       <c r="L41" s="0"/>
-      <c r="M41" s="0" t="b">
-        <v>0</v>
+      <c r="M41" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N41" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" s="0" t="b">
         <v>1</v>
@@ -2941,6 +3144,9 @@
         <v>1</v>
       </c>
       <c r="Q41" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2981,11 +3187,16 @@
       <c r="L42" s="0" t="n">
         <v>62</v>
       </c>
-      <c r="M42" s="0"/>
+      <c r="M42" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N42" s="0"/>
       <c r="O42" s="0"/>
       <c r="P42" s="0"/>
       <c r="Q42" s="0"/>
+      <c r="R42" s="0"/>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
@@ -3024,11 +3235,16 @@
       <c r="L43" s="0" t="n">
         <v>59</v>
       </c>
-      <c r="M43" s="0"/>
+      <c r="M43" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N43" s="0"/>
       <c r="O43" s="0"/>
       <c r="P43" s="0"/>
       <c r="Q43" s="0"/>
+      <c r="R43" s="0"/>
     </row>
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
@@ -3067,11 +3283,16 @@
       <c r="L44" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="M44" s="0"/>
+      <c r="M44" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N44" s="0"/>
       <c r="O44" s="0"/>
       <c r="P44" s="0"/>
       <c r="Q44" s="0"/>
+      <c r="R44" s="0"/>
     </row>
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
@@ -3110,11 +3331,16 @@
       <c r="L45" s="0" t="n">
         <v>54</v>
       </c>
-      <c r="M45" s="0"/>
+      <c r="M45" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N45" s="0"/>
       <c r="O45" s="0"/>
       <c r="P45" s="0"/>
       <c r="Q45" s="0"/>
+      <c r="R45" s="0"/>
     </row>
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
@@ -3153,11 +3379,16 @@
       <c r="L46" s="0" t="n">
         <v>52</v>
       </c>
-      <c r="M46" s="0"/>
+      <c r="M46" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N46" s="0"/>
       <c r="O46" s="0"/>
       <c r="P46" s="0"/>
       <c r="Q46" s="0"/>
+      <c r="R46" s="0"/>
     </row>
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
@@ -3196,11 +3427,16 @@
       <c r="L47" s="0" t="n">
         <v>48</v>
       </c>
-      <c r="M47" s="0"/>
+      <c r="M47" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N47" s="0"/>
       <c r="O47" s="0"/>
       <c r="P47" s="0"/>
       <c r="Q47" s="0"/>
+      <c r="R47" s="0"/>
     </row>
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
@@ -3239,11 +3475,16 @@
       <c r="L48" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="M48" s="0"/>
+      <c r="M48" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N48" s="0"/>
       <c r="O48" s="0"/>
       <c r="P48" s="0"/>
       <c r="Q48" s="0"/>
+      <c r="R48" s="0"/>
     </row>
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
@@ -3282,11 +3523,16 @@
       <c r="L49" s="0" t="n">
         <v>37</v>
       </c>
-      <c r="M49" s="0"/>
+      <c r="M49" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N49" s="0"/>
       <c r="O49" s="0"/>
       <c r="P49" s="0"/>
       <c r="Q49" s="0"/>
+      <c r="R49" s="0"/>
     </row>
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
@@ -3325,11 +3571,16 @@
       <c r="L50" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="M50" s="0"/>
+      <c r="M50" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N50" s="0"/>
       <c r="O50" s="0"/>
       <c r="P50" s="0"/>
       <c r="Q50" s="0"/>
+      <c r="R50" s="0"/>
     </row>
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
@@ -3368,11 +3619,16 @@
       <c r="L51" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="M51" s="0"/>
+      <c r="M51" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N51" s="0"/>
       <c r="O51" s="0"/>
       <c r="P51" s="0"/>
       <c r="Q51" s="0"/>
+      <c r="R51" s="0"/>
     </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2831,7 +2831,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2831,7 +2831,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2831,7 +2831,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2831,7 +2831,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2831,7 +2831,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2831,7 +2831,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2831,7 +2831,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2831,7 +2831,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2831,7 +2831,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2831,7 +2831,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/types/Task.xlsx
+++ b/data/samples/reports/sample_data_large/types/Task.xlsx
@@ -2831,7 +2831,7 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>
